--- a/FAQ 데이터.xlsx
+++ b/FAQ 데이터.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\Desktop\260608_오후\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AB16C03A-20C5-4849-B9C9-2DD25B609E16}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4484FE85-417B-4CA0-8AB2-574BFFDBF9AF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-105" yWindow="0" windowWidth="19410" windowHeight="15585" xr2:uid="{29E5C9DE-DA32-40AE-89BC-F0B11625A8D9}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="19" uniqueCount="16">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="19" uniqueCount="15">
   <si>
     <t>No</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -131,27 +131,50 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>총무</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>북시티 사옥 모바일 출입카드 발급 방법을 알려주세요.</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>신규입사자 명함 발급 방법을 알려주세요.</t>
+    <t>담당부서</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>명함 재발급 방법을 알려주세요.</t>
+    <r>
+      <t xml:space="preserve">에스원 모바일카드 발급 방법 안내해 드려요!
+우리 회사는 신청자가 직접 발급받는 방식이 아니라, 총무팀에서 권한을 부여하는 **'발급자 신청 방식'**을 이용하고 있습니다.
+아래 사옥 구분에 따라 담당자에게 요청하시면 빠르게 처리를 도와드립니다. </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Segoe UI Symbol"/>
+        <family val="2"/>
+      </rPr>
+      <t>😊</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+북시티 사옥 : 총무팀 담당자 (내선: 524) 연락
+상암동 사옥 : 총무팀 팀즈 채팅방으로 전달</t>
+    </r>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>명함 재발급 기준이 있는지 알려주세요.</t>
+    <t>상암동 사옥 모바일 출입카드 발급 방법을 알려주세요.</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>담당부서</t>
+    <t>에스원 모바일카드 발급 방법 안내해 드려요!
+상암동 사옥 : 총무팀 팀즈 채팅방으로 전달</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -159,7 +182,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="6" x14ac:knownFonts="1">
+  <fonts count="7" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -205,6 +228,12 @@
       <family val="3"/>
       <charset val="129"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Segoe UI Symbol"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="3">
@@ -636,7 +665,7 @@
         <v>9</v>
       </c>
       <c r="F1" s="4" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
     </row>
     <row r="2" spans="1:6" ht="409.5" customHeight="1" x14ac:dyDescent="0.3">
@@ -659,59 +688,55 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:6" ht="211.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="2">
         <v>2</v>
       </c>
       <c r="B3" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C3" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="D3" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="C3" s="2"/>
-      <c r="D3" s="3" t="s">
-        <v>11</v>
+      <c r="E3" s="6" t="s">
+        <v>12</v>
       </c>
-      <c r="E3" s="3"/>
       <c r="F3" s="3"/>
     </row>
-    <row r="4" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:6" ht="120.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="2">
         <v>3</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
-      <c r="C4" s="2"/>
+      <c r="C4" s="7" t="s">
+        <v>7</v>
+      </c>
       <c r="D4" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="E4" s="3"/>
-      <c r="F4" s="3"/>
-    </row>
-    <row r="5" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="2">
-        <v>4</v>
-      </c>
-      <c r="B5" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="C5" s="2"/>
-      <c r="D5" s="3" t="s">
         <v>13</v>
       </c>
+      <c r="E4" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="F4" s="3"/>
+    </row>
+    <row r="5" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A5" s="2"/>
+      <c r="B5" s="2"/>
+      <c r="C5" s="2"/>
+      <c r="D5" s="3"/>
       <c r="E5" s="3"/>
       <c r="F5" s="3"/>
     </row>
     <row r="6" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="2">
-        <v>5</v>
-      </c>
-      <c r="B6" s="2" t="s">
-        <v>10</v>
-      </c>
+      <c r="A6" s="2"/>
+      <c r="B6" s="2"/>
       <c r="C6" s="2"/>
-      <c r="D6" s="3" t="s">
-        <v>14</v>
-      </c>
+      <c r="D6" s="3"/>
       <c r="E6" s="3"/>
       <c r="F6" s="3"/>
     </row>
